--- a/naver-place-crawler/results_nail/창원_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/창원_네일샵.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="37" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,38 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한하루네일</t>
+          <t>RELA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nang_ny@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>cto@handsos.com</t>
-        </is>
-      </c>
+          <t>ejh200024@naver.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1364-8995</t>
+          <t>0507-1399-6318</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 마디미로43번길 10 2층 한하루헤어 내</t>
+          <t>경남 창원시 성산구 원이대로 320 E동 303호 푸쳐핸썹</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/13/bizes/193143/items/4667553?area=ple</t>
+          <t>https://www.instagram.com/pyhu_nail?igsh=bDBiMW5xMnowYXA5</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -605,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -615,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40lj9</t>
+          <t>https://talk.naver.com/ct/w4k4ta</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -629,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>101</v>
+        <v>338</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>707</v>
       </c>
       <c r="R2" t="n">
-        <v>106</v>
+        <v>1045</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -644,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1767230739</t>
+          <t>59090072</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1767230739</t>
+          <t>https://m.place.naver.com/place/59090072</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -666,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>무니크네일&amp;왁싱</t>
+          <t>메인네일 창원상남점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>gksdkfhd@naver.com</t>
+          <t>main_nail@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1305-4986</t>
+          <t>0507-1399-1378</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 용지로 110 동광뷰엘 1층 107호</t>
+          <t>경남 창원시 성산구 상남로 126 세종엠필드 2층 210호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/munique__nail</t>
+          <t>https://www.instagram.com/main_nail/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -713,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4j809</t>
+          <t>https://talk.naver.com/ct/wu0rles</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>870</v>
+        <v>2606</v>
       </c>
       <c r="Q3" t="n">
-        <v>1032</v>
+        <v>230</v>
       </c>
       <c r="R3" t="n">
-        <v>1902</v>
+        <v>2836</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -742,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1487347547</t>
+          <t>13570858</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1487347547</t>
+          <t>https://m.place.naver.com/place/13570858</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -764,34 +760,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>디유네일</t>
+          <t>네일베베</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>zena2_@naver.com</t>
+          <t>jisunlove2@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1349-8465</t>
+          <t>0507-1367-5026</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 동산로73번길 5 디유네일</t>
+          <t>경남 창원시 성산구 원이대로 672 대고빌딩 4층 네일베베</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xlXdxexj</t>
+          <t>http://instagram.com/nailbebe_</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -811,12 +807,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4uccg</t>
+          <t>https://talk.naver.com/ct/w450hv</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -825,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>406</v>
+        <v>828</v>
       </c>
       <c r="Q4" t="n">
-        <v>745</v>
+        <v>77</v>
       </c>
       <c r="R4" t="n">
-        <v>1151</v>
+        <v>905</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -840,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1352280729</t>
+          <t>1101122955</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1352280729</t>
+          <t>https://m.place.naver.com/place/1101122955</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -923,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="Q5" t="n">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R5" t="n">
-        <v>1728</v>
+        <v>1722</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -948,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -960,39 +956,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>붕어네일&amp;속눈썹</t>
+          <t>메인네일 창원시티세븐점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lo_ve90@naver.com</t>
+          <t>mainnail-city7@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1382-5363</t>
+          <t>0507-1443-1269</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 마디미로38번길 11 2층 225호</t>
+          <t>경남 창원시 성산구 원이대로 320 더시티세븐 1층 G동 125호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>http://붕어네일속눈썹.kr</t>
+          <t>https://www.instagram.com/main_nail/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1007,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4x6jn</t>
+          <t>https://talk.naver.com/ct/w40lul</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1021,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>260</v>
+        <v>2801</v>
       </c>
       <c r="Q6" t="n">
-        <v>538</v>
+        <v>43</v>
       </c>
       <c r="R6" t="n">
-        <v>798</v>
+        <v>2844</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1539843695</t>
+          <t>1860828126</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1539843695</t>
+          <t>https://m.place.naver.com/place/1860828126</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1058,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RELA</t>
+          <t>닥터페디 본점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ejh200024@naver.com</t>
+          <t>nail-it@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1399-6318</t>
+          <t>0507-1441-5541</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 원이대로 320 E동 303호 푸쳐핸썹</t>
+          <t>경남 창원시 성산구 원이대로 320 시티세븐 쇼핑몰 W-210호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pyhu_nail?igsh=bDBiMW5xMnowYXA5</t>
+          <t>https://youtube.com/@Dr.PEDI_</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4k4ta</t>
+          <t>https://talk.naver.com/ct/w5zweg</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1119,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>337</v>
+        <v>837</v>
       </c>
       <c r="Q7" t="n">
-        <v>693</v>
+        <v>1178</v>
       </c>
       <c r="R7" t="n">
-        <v>1030</v>
+        <v>2015</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>59090072</t>
+          <t>858723184</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/59090072</t>
+          <t>https://m.place.naver.com/place/858723184</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1156,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>닥터페디 본점</t>
+          <t>엔피케어 창원진해점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nail-it@naver.com</t>
+          <t>np_care@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1441-5541</t>
+          <t>0507-1465-3224</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 원이대로 320 시티세븐 쇼핑몰 W-210호</t>
+          <t>경남 창원시 진해구 풍호로3번길 4 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://youtube.com/@Dr.PEDI_</t>
+          <t>https://blog.naver.com/np_care</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1193,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1203,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zweg</t>
+          <t>https://talk.naver.com/ct/w4qy8w</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1217,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>837</v>
+        <v>467</v>
       </c>
       <c r="Q8" t="n">
-        <v>1177</v>
+        <v>195</v>
       </c>
       <c r="R8" t="n">
-        <v>2014</v>
+        <v>662</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1232,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>858723184</t>
+          <t>1245037591</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/858723184</t>
+          <t>https://m.place.naver.com/place/1245037591</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1254,39 +1250,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엔피케어 창원진해점</t>
+          <t>더블류네일&amp;오로지푸스 창원마산합포점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>np_care@naver.com</t>
+          <t>nailardi@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1465-3224</t>
+          <t>0507-1487-0529</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경남 창원시 진해구 풍호로3번길 4 4층</t>
+          <t>경남 창원시 마산합포구 가포로 8 6층, 더블류뷰티</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/np_care</t>
+          <t>https://naver.me/5dx70WaU</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1301,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4qy8w</t>
+          <t>https://talk.naver.com/ct/w48iao</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,17 +1307,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>467</v>
+        <v>277</v>
       </c>
       <c r="Q9" t="n">
-        <v>192</v>
+        <v>57</v>
       </c>
       <c r="R9" t="n">
-        <v>659</v>
+        <v>334</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1330,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1245037591</t>
+          <t>1815575944</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245037591</t>
+          <t>https://m.place.naver.com/place/1815575944</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
@@ -1352,34 +1348,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더블류네일&amp;오로지푸스 창원마산합포점</t>
+          <t>예지량네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nailardi@naver.com</t>
+          <t>dbsghrhkdvos@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1487-0529</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경남 창원시 마산합포구 가포로 8 6층, 더블류뷰티</t>
+          <t>경남 창원시 의창구 태복산로13번길 33 국도하이츠빌라 1층 103호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://naver.me/5dx70WaU</t>
+          <t>https://www.instagram.com/yejiryangnail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1399,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48iao</t>
+          <t>https://talk.naver.com/ct/w4dm1o</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>277</v>
+        <v>122</v>
       </c>
       <c r="Q10" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="R10" t="n">
-        <v>334</v>
+        <v>139</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1428,115 +1420,311 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1815575944</t>
+          <t>1422581076</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1815575944</t>
+          <t>https://m.place.naver.com/place/1422581076</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>찌개,전골</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>윌슨988 창원상남점</t>
+          <t>네일디어블리스 창원도계점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tando7656@naver.com</t>
+          <t>thddnwjd45@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1411-3302</t>
+          <t>0507-1339-5119</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>경남 창원시 의창구 도계로163번길 2 1층 101호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nail_dear.bliss/</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4d8ky</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>109</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>24</v>
+      </c>
+      <c r="R11" t="n">
+        <v>133</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1375385682</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1375385682</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>속눈썹증모,연장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>더블류뷰티 속눈썹&amp;왁싱&amp;눈썹 창원마산점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>double-ryu@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1340-1816</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경남 창원시 마산합포구 가포로 8 601호 더블류뷰티</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/double-ryu</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4nyq3</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1407</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>125</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1532</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1237855657</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1237855657</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>찌개,전골</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>윌슨988 창원상남점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>tando7656@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1411-3302</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>경남 창원시 성산구 마디미로 28 상남재래시장 C-208</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>https://blog.naver.com/tando7656</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w42ba3</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>1124</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>749</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1873</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1138</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>750</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1888</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>37591615</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/37591615</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/창원_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/창원_네일샵.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
@@ -564,34 +564,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RELA</t>
+          <t>한하루네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ejh200024@naver.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>nang_ny@naver.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>cto@handsos.com</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1399-6318</t>
+          <t>0507-1364-8995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 원이대로 320 E동 303호 푸쳐핸썹</t>
+          <t>경남 창원시 성산구 마디미로43번길 10 2층 한하루헤어 내</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pyhu_nail?igsh=bDBiMW5xMnowYXA5</t>
+          <t>https://m.booking.naver.com/booking/13/bizes/193143/items/4667553?area=ple</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +605,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +615,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4k4ta</t>
+          <t>https://talk.naver.com/ct/w40lj9</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +629,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>338</v>
+        <v>100</v>
       </c>
       <c r="Q2" t="n">
-        <v>707</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>1045</v>
+        <v>105</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +644,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>59090072</t>
+          <t>1767230739</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/59090072</t>
+          <t>https://m.place.naver.com/place/1767230739</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2606</v>
+        <v>2615</v>
       </c>
       <c r="Q3" t="n">
         <v>230</v>
       </c>
       <c r="R3" t="n">
-        <v>2836</v>
+        <v>2845</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +752,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -760,29 +764,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일베베</t>
+          <t>메인네일 창원시티세븐점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jisunlove2@naver.com</t>
+          <t>mainnail-city7@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1367-5026</t>
+          <t>0507-1443-1269</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 원이대로 672 대고빌딩 4층 네일베베</t>
+          <t>경남 창원시 성산구 원이대로 320 더시티세븐 1층 G동 125호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://instagram.com/nailbebe_</t>
+          <t>https://www.instagram.com/main_nail/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +811,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w450hv</t>
+          <t>https://talk.naver.com/ct/w40lul</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +825,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>828</v>
+        <v>2804</v>
       </c>
       <c r="Q4" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="R4" t="n">
-        <v>905</v>
+        <v>2847</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +840,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1101122955</t>
+          <t>1860828126</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1101122955</t>
+          <t>https://m.place.naver.com/place/1860828126</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,34 +862,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>레푸스 창원상남점</t>
+          <t>코코미뷰티</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ohjinga48@naver.com</t>
+          <t>marinebong0429@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1373-2924</t>
+          <t>0507-1335-3135</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 마디미로16번길 9 5층 502호</t>
+          <t>경남 창원시 성산구 마디미로27번길 14 3층 코코미뷰티</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ohjinga48</t>
+          <t>http://pf.kakao.com/_WDxgcxj</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,7 +899,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,12 +909,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47gnk</t>
+          <t>https://talk.naver.com/ct/w4trt8</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1019</v>
+        <v>632</v>
       </c>
       <c r="Q5" t="n">
-        <v>703</v>
+        <v>258</v>
       </c>
       <c r="R5" t="n">
-        <v>1722</v>
+        <v>890</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +938,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>37818153</t>
+          <t>1600398229</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37818153</t>
+          <t>https://m.place.naver.com/place/1600398229</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -956,29 +960,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>메인네일 창원시티세븐점</t>
+          <t>RELA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mainnail-city7@naver.com</t>
+          <t>ejh200024@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1443-1269</t>
+          <t>0507-1399-6318</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 원이대로 320 더시티세븐 1층 G동 125호</t>
+          <t>경남 창원시 성산구 원이대로 320 E동 303호 푸쳐핸썹</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/main_nail/</t>
+          <t>https://www.instagram.com/pyhu_nail?igsh=bDBiMW5xMnowYXA5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1007,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40lul</t>
+          <t>https://talk.naver.com/ct/w4k4ta</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2801</v>
+        <v>339</v>
       </c>
       <c r="Q6" t="n">
-        <v>43</v>
+        <v>711</v>
       </c>
       <c r="R6" t="n">
-        <v>2844</v>
+        <v>1050</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1036,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1860828126</t>
+          <t>59090072</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1860828126</t>
+          <t>https://m.place.naver.com/place/59090072</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1058,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>닥터페디 본점</t>
+          <t>레푸스 창원상남점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nail-it@naver.com</t>
+          <t>ohjinga48@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1441-5541</t>
+          <t>0507-1373-2924</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 원이대로 320 시티세븐 쇼핑몰 W-210호</t>
+          <t>경남 창원시 성산구 마디미로16번길 9 5층 502호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://youtube.com/@Dr.PEDI_</t>
+          <t>https://blog.naver.com/ohjinga48</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,7 +1095,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1105,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zweg</t>
+          <t>https://talk.naver.com/ct/w47gnk</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>837</v>
+        <v>1017</v>
       </c>
       <c r="Q7" t="n">
-        <v>1178</v>
+        <v>703</v>
       </c>
       <c r="R7" t="n">
-        <v>2015</v>
+        <v>1720</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1134,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>858723184</t>
+          <t>37818153</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/858723184</t>
+          <t>https://m.place.naver.com/place/37818153</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1156,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엔피케어 창원진해점</t>
+          <t>까사벨르네일속눈썹 홈플러스진해점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>np_care@naver.com</t>
+          <t>mnmy99@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1465-3224</t>
+          <t>0507-1346-5243</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경남 창원시 진해구 풍호로3번길 4 4층</t>
+          <t>경남 창원시 진해구 충장로 356 진해홈플러스 2층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/np_care</t>
+          <t>https://open.kakao.com/o/sWIntTFg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,22 +1193,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4qy8w</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>467</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="n">
-        <v>195</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>662</v>
+        <v>25</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1245037591</t>
+          <t>1034880464</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1245037591</t>
+          <t>https://m.place.naver.com/place/1034880464</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1250,44 +1250,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>더블류네일&amp;오로지푸스 창원마산합포점</t>
+          <t>닥터페디 본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nailardi@naver.com</t>
+          <t>nail-it@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1487-0529</t>
+          <t>0507-1441-5541</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경남 창원시 마산합포구 가포로 8 6층, 더블류뷰티</t>
+          <t>경남 창원시 성산구 원이대로 320 시티세븐 쇼핑몰 W-210호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://naver.me/5dx70WaU</t>
+          <t>https://youtube.com/@Dr.PEDI_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48iao</t>
+          <t>https://talk.naver.com/ct/w5zweg</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>277</v>
+        <v>837</v>
       </c>
       <c r="Q9" t="n">
-        <v>57</v>
+        <v>1181</v>
       </c>
       <c r="R9" t="n">
-        <v>334</v>
+        <v>2018</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1815575944</t>
+          <t>858723184</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1815575944</t>
+          <t>https://m.place.naver.com/place/858723184</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1348,30 +1348,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>예지량네일</t>
+          <t>더블류네일&amp;오로지푸스 창원마산합포점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dbsghrhkdvos@naver.com</t>
+          <t>nailardi@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1487-0529</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경남 창원시 의창구 태복산로13번길 33 국도하이츠빌라 1층 103호</t>
+          <t>경남 창원시 마산합포구 가포로 8 6층, 더블류뷰티</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yejiryangnail</t>
+          <t>https://naver.me/5dx70WaU</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1391,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dm1o</t>
+          <t>https://talk.naver.com/ct/w48iao</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>122</v>
+        <v>278</v>
       </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="R10" t="n">
-        <v>139</v>
+        <v>335</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1422581076</t>
+          <t>1815575944</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1422581076</t>
+          <t>https://m.place.naver.com/place/1815575944</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1446,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일디어블리스 창원도계점</t>
+          <t>예지량네일</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>thddnwjd45@naver.com</t>
+          <t>dbsghrhkdvos@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1339-5119</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 의창구 도계로163번길 2 1층 101호</t>
+          <t>경남 창원시 의창구 태복산로13번길 33 국도하이츠빌라 1층 103호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_dear.bliss/</t>
+          <t>https://www.instagram.com/yejiryangnail</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4d8ky</t>
+          <t>https://talk.naver.com/ct/w4dm1o</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,213 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1375385682</t>
+          <t>1422581076</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1375385682</t>
+          <t>https://m.place.naver.com/place/1422581076</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>속눈썹증모,연장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>더블류뷰티 속눈썹&amp;왁싱&amp;눈썹 창원마산점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>double-ryu@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1340-1816</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경남 창원시 마산합포구 가포로 8 601호 더블류뷰티</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/double-ryu</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4nyq3</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1407</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>125</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1532</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1237855657</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1237855657</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>찌개,전골</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>윌슨988 창원상남점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>tando7656@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1411-3302</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경남 창원시 성산구 마디미로 28 상남재래시장 C-208</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/tando7656</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42ba3</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1138</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>750</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1888</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>37591615</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37591615</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/창원_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/창원_네일샵.xlsx
@@ -421,8 +421,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2804</v>
+        <v>2802</v>
       </c>
       <c r="Q4" t="n">
         <v>43</v>
       </c>
       <c r="R4" t="n">
-        <v>2847</v>
+        <v>2845</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -862,34 +862,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>코코미뷰티</t>
+          <t>RELA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>marinebong0429@naver.com</t>
+          <t>ejh200024@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1335-3135</t>
+          <t>0507-1399-6318</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 마디미로27번길 14 3층 코코미뷰티</t>
+          <t>경남 창원시 성산구 원이대로 320 E동 303호 푸쳐핸썹</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_WDxgcxj</t>
+          <t>https://www.instagram.com/pyhu_nail?igsh=bDBiMW5xMnowYXA5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4trt8</t>
+          <t>https://talk.naver.com/ct/w4k4ta</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>632</v>
+        <v>339</v>
       </c>
       <c r="Q5" t="n">
-        <v>258</v>
+        <v>711</v>
       </c>
       <c r="R5" t="n">
-        <v>890</v>
+        <v>1050</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -938,12 +938,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1600398229</t>
+          <t>59090072</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1600398229</t>
+          <t>https://m.place.naver.com/place/59090072</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -960,29 +960,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RELA</t>
+          <t>레푸스 창원상남점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ejh200024@naver.com</t>
+          <t>ohjinga48@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1399-6318</t>
+          <t>0507-1373-2924</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 원이대로 320 E동 303호 푸쳐핸썹</t>
+          <t>경남 창원시 성산구 마디미로16번길 9 5층 502호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pyhu_nail?igsh=bDBiMW5xMnowYXA5</t>
+          <t>https://blog.naver.com/ohjinga48</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4k4ta</t>
+          <t>https://talk.naver.com/ct/w47gnk</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>339</v>
+        <v>1017</v>
       </c>
       <c r="Q6" t="n">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="R6" t="n">
-        <v>1050</v>
+        <v>1721</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>59090072</t>
+          <t>37818153</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/59090072</t>
+          <t>https://m.place.naver.com/place/37818153</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1058,29 +1058,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>레푸스 창원상남점</t>
+          <t>데일리네일 창원상남본점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ohjinga48@naver.com</t>
+          <t>changwondailynail@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1373-2924</t>
+          <t>0507-1318-8778</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 마디미로16번길 9 5층 502호</t>
+          <t>경남 창원시 성산구 마디미로43번길 10 모아엔트몰 3층 302호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ohjinga48</t>
+          <t>https://blog.naver.com/changwondailynail</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w47gnk</t>
+          <t>https://talk.naver.com/ct/w5zfw1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1017</v>
+        <v>983</v>
       </c>
       <c r="Q7" t="n">
-        <v>703</v>
+        <v>45</v>
       </c>
       <c r="R7" t="n">
-        <v>1720</v>
+        <v>1028</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37818153</t>
+          <t>1282681028</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37818153</t>
+          <t>https://m.place.naver.com/place/1282681028</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1156,29 +1156,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>까사벨르네일속눈썹 홈플러스진해점</t>
+          <t>닥터페디 본점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mnmy99@naver.com</t>
+          <t>nail-it@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1346-5243</t>
+          <t>0507-1441-5541</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경남 창원시 진해구 충장로 356 진해홈플러스 2층</t>
+          <t>경남 창원시 성산구 원이대로 320 시티세븐 쇼핑몰 W-210호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sWIntTFg</t>
+          <t>https://youtube.com/@Dr.PEDI_</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1198,13 +1198,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zweg</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1213,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>24</v>
+        <v>837</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>1181</v>
       </c>
       <c r="R8" t="n">
-        <v>25</v>
+        <v>2018</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1232,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1034880464</t>
+          <t>858723184</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1034880464</t>
+          <t>https://m.place.naver.com/place/858723184</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1254,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>닥터페디 본점</t>
+          <t>엔피케어 창원진해점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nail-it@naver.com</t>
+          <t>np_care@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1441-5541</t>
+          <t>0507-1465-3224</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 원이대로 320 시티세븐 쇼핑몰 W-210호</t>
+          <t>경남 창원시 진해구 풍호로3번길 4 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/@Dr.PEDI_</t>
+          <t>https://blog.naver.com/np_care</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1291,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1301,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zweg</t>
+          <t>https://talk.naver.com/ct/w4qy8w</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1315,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>837</v>
+        <v>468</v>
       </c>
       <c r="Q9" t="n">
-        <v>1181</v>
+        <v>195</v>
       </c>
       <c r="R9" t="n">
-        <v>2018</v>
+        <v>663</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1330,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>858723184</t>
+          <t>1245037591</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/858723184</t>
+          <t>https://m.place.naver.com/place/1245037591</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,34 +1352,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더블류네일&amp;오로지푸스 창원마산합포점</t>
+          <t>예지량네일</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nailardi@naver.com</t>
+          <t>dbsghrhkdvos@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1487-0529</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경남 창원시 마산합포구 가포로 8 6층, 더블류뷰티</t>
+          <t>경남 창원시 의창구 태복산로13번길 33 국도하이츠빌라 1층 103호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://naver.me/5dx70WaU</t>
+          <t>https://www.instagram.com/yejiryangnail</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w48iao</t>
+          <t>https://talk.naver.com/ct/w4dm1o</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>278</v>
+        <v>122</v>
       </c>
       <c r="Q10" t="n">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="R10" t="n">
-        <v>335</v>
+        <v>139</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1815575944</t>
+          <t>1422581076</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1815575944</t>
+          <t>https://m.place.naver.com/place/1422581076</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,30 +1441,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>네일아트,네일샵</t>
+          <t>찌개,전골</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>예지량네일</t>
+          <t>윌슨988 창원상남점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dbsghrhkdvos@naver.com</t>
+          <t>tando7656@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1411-3302</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 의창구 태복산로13번길 33 국도하이츠빌라 1층 103호</t>
+          <t>경남 창원시 성산구 마디미로 28 상남재래시장 C-208</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yejiryangnail</t>
+          <t>https://blog.naver.com/tando7656</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4dm1o</t>
+          <t>https://talk.naver.com/ct/w42ba3</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,17 +1503,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>122</v>
+        <v>1153</v>
       </c>
       <c r="Q11" t="n">
-        <v>17</v>
+        <v>751</v>
       </c>
       <c r="R11" t="n">
-        <v>139</v>
+        <v>1904</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1422581076</t>
+          <t>37591615</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1422581076</t>
+          <t>https://m.place.naver.com/place/37591615</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_nail/창원_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/창원_네일샵.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -654,7 +654,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/main_nail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="Q3" t="n">
         <v>230</v>
       </c>
       <c r="R3" t="n">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/main_nail/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pyhu_nail?igsh=bDBiMW5xMnowYXA5</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -926,10 +926,10 @@
         <v>339</v>
       </c>
       <c r="Q5" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="R5" t="n">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -982,7 +982,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ohjinga48</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1021,13 +1021,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="Q6" t="n">
         <v>704</v>
       </c>
       <c r="R6" t="n">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/changwondailynail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="Q7" t="n">
         <v>45</v>
       </c>
       <c r="R7" t="n">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="Q8" t="n">
         <v>1181</v>
       </c>
       <c r="R8" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/np_care</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yejiryangnail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1434,41 +1434,41 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>찌개,전골</t>
+          <t>네일아트,네일샵</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>윌슨988 창원상남점</t>
+          <t>까사벨르네일속눈썹 홈플러스진해점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tando7656@naver.com</t>
+          <t>mnmy99@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1411-3302</t>
+          <t>0507-1346-5243</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 마디미로 28 상남재래시장 C-208</t>
+          <t>경남 창원시 진해구 충장로 356 진해홈플러스 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tando7656</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1478,42 +1478,38 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w42ba3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1153</v>
+        <v>24</v>
       </c>
       <c r="Q11" t="n">
-        <v>751</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1904</v>
+        <v>25</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,17 +1518,115 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37591615</t>
+          <t>1034880464</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37591615</t>
+          <t>https://m.place.naver.com/place/1034880464</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>뷰티앤유</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hun3915@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1344-0229</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경남 창원시 성산구 상남로 107 메종드테라스 2층 225호 뷰티앤유</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4gpqd</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1194</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>79</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1273</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1023534456</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1023534456</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
